--- a/analysis/coding_worksheets/決策群組_#102.xlsx
+++ b/analysis/coding_worksheets/決策群組_#102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AH52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,145 +451,150 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt2</t>
         </is>
@@ -618,17 +623,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -705,6 +712,9 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,17 +741,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>我選 Amy</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -818,6 +830,9 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>我選 Sally</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -931,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,17 +977,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>我看nancy無論是專業能力或是管理能力好像都蠻不錯的，在業界工作的資歷也挺資深的</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1044,6 +1066,9 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,19 +1095,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>我覺得Amy最適合，因為她曾擔任公司爭議解決委員會，並獲得良好評價。
 Sally 會利用團隊組織政治為自己某利，會影響上下屬對他的觀感
 Nancy 會不記得表揚他人貢獻，會大大影響團隊氣氛</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1159,6 +1186,9 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1185,17 +1215,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>但5年來沒有從公司內部選出Amy或Nancy來當CFO，代表他們的能力還不夠吧，所以我選擇Sally說不定可以為公司帶來不一樣的火花。</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1272,6 +1304,9 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,17 +1333,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>而且Sally也有在倫敦的財務部門服務過兩年，會有不同的觀點。</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1385,6 +1422,9 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1411,18 +1451,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>以現有的資料來看，我認為並沒有明確指出能力不夠
 依照資料顯示每個人都各自有自己的經驗，我認為這個職位應該以個人特質來選擇誰帶領公司比較適合，需要大量的溝通合作</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1499,6 +1541,9 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1525,17 +1570,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>我想作為公司高層，準時應該要是基本的態度，不然這樣跟別人開會時也會影響公司觀感。nancy雖然會不記得表揚他人貢獻，但至少他很公平，代表他的決策能讓人信服。sally雖然來自別的公司，但不能確定他能不能快速了解這間公司</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1612,6 +1659,9 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1638,10 +1688,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>目前小組討論重點整理如下：  
 - Nancy 的專業與管理能力、資歷被肯定，但有成員擔心她不善於表揚他人，可能影響團隊氣氛。
@@ -1650,9 +1705,6 @@
 目前針對「國際視野」部分，僅 Sally 的倫敦經歷被提及；而「合作特質」與「個人經歷」兩項，成員看法尚未完全彙整。是否還需要考量三位候選人在跨部門合作、誠信、溝通等特質上的具體表現？還有沒有成員知道更多關於候選人國際合作或領導團隊的具體事例呢？</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1729,6 +1781,9 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1755,17 +1810,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>nancy有曾經在美國證券交易委員會的工作經歷，我想這對他的國際視野會有很大的加分</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1842,6 +1899,9 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,17 +1928,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>我同意nancy 的經歷對國際視野是加分的</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1955,6 +2017,9 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1981,17 +2046,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>而且既然要能夠帶領團隊並且跨部門合作，我想嚴格和公平都是有其重要性的個人特質</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -2068,6 +2135,9 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2094,19 +2164,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>我覺得以經歷的部分，三位候選人其實不分上下，但在個人特質的部分，Nancy在專案完成後，不記得去表揚他人的貢獻，某種程度上是沒辦法帶到員工的心，及增加團隊向心力。
 而Sally及Amy皆會注重細節，雖然被員工抱怨冷漠疏遠，但我想是發生在過程中而已吧。
 然後Sally是一位優秀的公開演講者，我想不管是對外或對內都有良好的形象。</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -2183,6 +2255,9 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2209,17 +2284,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -2296,6 +2373,9 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2322,17 +2402,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2409,6 +2491,9 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2435,17 +2520,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2522,6 +2609,9 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2548,17 +2638,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>我同意Sally是一位優秀的公開演講者，但這個特質可能更適合其他職位，因為財務長通常不是代表公司對外發聲的人</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2635,6 +2727,9 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2661,17 +2756,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>我的資料顯示員工說Sally 善於利用利用組織政治為自己某利，且來自競爭對手的公司，可能很難帶領整個團隊的合作氣氛</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -2748,6 +2845,9 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2774,10 +2874,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>彙整目前討論重點：  
 - Nancy 除了業界資歷，也有美國證券交易委員會的經歷，國際視野受到肯定，且以嚴格與公平著稱。
@@ -2786,9 +2891,6 @@
 目前針對「領導合作」的實際案例，以及三位候選人在誠信、跨部門合作、激勵團隊向心力上的表現，討論還未十分具體。是否還需要成員補充更多與這些面向有關的具體經驗或觀察？還有沒有其他成員知道候選人在實際領導團隊時遇過的挑戰與成果？</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -2865,6 +2967,9 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2891,17 +2996,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>我收到的資料並沒有顯示出Sally善於利用組織政治為自己牟利，如果真的有這樣的狀況，我想我會改推薦Amy。</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -2978,6 +3085,9 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3004,17 +3114,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>我這邊並未收到Amy 曾任爭議解決委員會的資訊，如果屬實，那我覺得amy也蠻有資格的，但在選他之前，可能要跟他溝通一下他的遲到壞習慣需要改善</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -3091,6 +3203,9 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3117,17 +3232,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>作為人資長，sally算是蠻明顯違背競業條款的人吧，大部分科技公司都不希望員工來自主要競爭對手，而且一旦任命sally，等於就是變相讓業界覺得我們沒有商業道德</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -3204,6 +3321,9 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3230,17 +3350,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>我的資料顯示Amy 不是一個鼓舞人心的演講者而已，如果遲到習慣屬實，我覺得可以利用溝通方式安排會議的進程，或請他提早通知會遲到等等，並盡量改掉此習慣</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -3317,6 +3439,9 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3343,18 +3468,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>我沒收到Amy有遲到的壞習慣，如果屬實我覺得是需要請他改善的。
 然後我不認同Nancy是因為他不記得表揚他人的貢獻，這會讓公司沒有向心力，可能會讓員工覺得自己是免洗筷，用完即丟。</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -3431,6 +3558,9 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3457,17 +3587,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>這樣看來我們收到的資訊其實都有些遺漏，如果有不確定的部分也許可以一起核對事實</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -3544,6 +3676,9 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3570,10 +3705,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>目前討論摘要如下：  
 - Nancy 具備國際經歷（美國證券交易委員會），嚴格公平，但較少表揚他人，對團隊向心力可能有影響。
@@ -3582,9 +3722,6 @@
 目前部分資訊來源存在出入或遺漏，是否需要大家再次確認手中資訊，或彙整每位候選人在財務專業、領導合作、國際視野、個人經歷、合作特質等條件上的具體事證？還有沒有成員能補充更明確的案例，以協助團隊做出更全面的評估？</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
@@ -3661,6 +3798,9 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3687,17 +3827,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>我可以問問你們那邊關於amy的個人特質敘述嗎</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3774,6 +3916,9 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3800,17 +3945,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>我這邊是員工抱怨他很冷漠疏遠、注重細節。</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -3887,6 +4034,9 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3913,19 +4063,21 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>個人特質:
 不是一個鼓舞人心的演講者
 注重細節</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
@@ -4002,6 +4154,9 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4028,19 +4183,21 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>這是我收到的
 有開會遲到的習慣
 注重細節</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -4117,6 +4274,9 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4143,17 +4303,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>那nancy的呢？</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -4230,6 +4392,9 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4256,17 +4421,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>專案完成 不會表揚他人的貢獻</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -4343,6 +4510,9 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4369,10 +4539,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>目前大家提供的 Nancy 個人特質資訊彙整如下：  
 - 專案完成後不會表揚他人貢獻，可能影響團隊向心力。
@@ -4381,9 +4556,6 @@
 目前針對 Nancy 的「合作特質」與「激勵團隊」具體事例，尚未有更多細節。是否還需要成員補充 Nancy 在跨部門協作、團隊溝通或激勵員工方面的真實經歷？還有沒有其他成員知道 Nancy 如何處理團隊衝突或促進合作的案例？</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -4460,6 +4632,9 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4486,17 +4661,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>想問問營運長那邊看到的呢</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
@@ -4573,6 +4750,9 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4599,18 +4779,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>一樣
 加上對組織政治有好的觀察力</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
@@ -4687,6 +4869,9 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4713,17 +4898,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>那這樣看來目前應該就是amy nancy二選一，對嗎大家</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
@@ -4800,6 +4987,9 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4826,18 +5016,20 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>比起Nancy 會不記得表揚他人，確實會比遲到更影響團隊氣氛
 冷漠疏遠或許跟部會鼓舞人心有點雷同? 都屬於不太會表達感受，不過至少在專業和做事態度上沒有太大疑慮?</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
@@ -4914,6 +5106,9 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4940,17 +5135,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>認同</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
@@ -5027,6 +5224,9 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5053,17 +5253,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>同意</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
@@ -5140,6 +5342,9 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5166,10 +5371,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>目前大家共識整理如下：  
 - Sally 因競業條款及組織政治等疑慮，已較少被考慮。
@@ -5179,9 +5389,6 @@
 目前在「領導合作」及「合作特質」的具體案例仍不多。是否還需要補充兩人在帶領團隊、跨部門溝通或激勵員工方面的實際事例？還有沒有成員知道她們在壓力下或遇到衝突時的處理方式？</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
@@ -5258,6 +5465,9 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5284,17 +5494,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>我也同意，遲到算是比較好解決的問題</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
@@ -5371,6 +5583,9 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5397,17 +5612,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
@@ -5484,6 +5701,9 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5510,17 +5730,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
@@ -5597,6 +5819,9 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5623,17 +5848,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
@@ -5710,6 +5937,9 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5736,17 +5966,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
@@ -5823,6 +6055,9 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5849,17 +6084,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
@@ -5936,6 +6173,9 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5962,17 +6202,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
@@ -6049,6 +6291,9 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6075,17 +6320,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
@@ -6162,6 +6409,9 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6188,17 +6438,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
@@ -6275,6 +6527,9 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6301,17 +6556,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
@@ -6388,6 +6645,9 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>0</v>
       </c>
     </row>
